--- a/content/Question Bank/Coding Questions/Unit 8 - Functions/Unit 8 - Functions - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 8 - Functions/Unit 8 - Functions - Coding Questions.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -596,13 +596,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Write a function that returns the square of a number, then use it to print the square of the number that is read from input.
+          <t>Meena is helping her father lay tiles in their square courtyard in Mysuru. If one side needs a certain number of tiles, the total number of tiles is that number multiplied by itself. Write a function named `square` that takes one number and returns its square. Then read a number from input, call your function, and print the result.
 ### Input Format
 - Line 1: A number
 ### Output Format
 ```
 25
 ```
+### Example Walkthrough
+For the sample input, the number read is 5. The function multiplies 5 by itself, giving 5 x 5 = 25, so the program prints `25`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -723,6 +725,15 @@
       <c r="AE2" t="inlineStr">
         <is>
           <t>10000</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>def square(x):
+    # write your code here
+    pass
+n = int(input())
+print(square(n))</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -742,7 +753,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Write a function that returns the sum of two numbers. Read two numbers and print their sum using the function.
+          <t>Arjun buys a samosa and a cup of tea at the college canteen, and the cashier quickly adds the two prices to tell him the bill. Write a function named `add` that takes two numbers and returns their sum. Read two numbers from input, call your function, and print the total.
 ### Input Format
 - Line 1: First number
 - Line 2: Second number
@@ -750,6 +761,8 @@
 ```
 7
 ```
+### Example Walkthrough
+For the sample input, the two numbers are 3 and 4. The function returns 3 + 4 = 7, so the program prints `7`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -877,6 +890,16 @@
       <c r="AE3" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>def add(a, b):
+    # write your code here
+    pass
+x = int(input())
+y = int(input())
+print(add(x, y))</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -897,7 +920,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Write a function that returns the larger of two numbers. Read two numbers and print the larger one.
+          <t>Priya and Rahul compare their marks after the weekly Python quiz, and their teacher announces only the higher score. Write a function named `maximum` that takes two numbers and returns the larger one. Read two numbers from input, call your function, and print the larger number.
 ### Input Format
 - Line 1: First number
 - Line 2: Second number
@@ -905,6 +928,8 @@
 ```
 9
 ```
+### Example Walkthrough
+For the sample input, the two numbers are 3 and 9. Since 9 is greater than 3, the function returns `9` and the program prints `9`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1034,13 +1059,23 @@
           <t>1000</t>
         </is>
       </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>def bigger(a, b):
+    # write your code here
+    pass
+x = int(input())
+y = int(input())
+print(bigger(x, y))</t>
+        </is>
+      </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>def bigger(a, b):
+          <t>def maximum(a, b):
     return a if a &gt;= b else b
 x = int(input())
 y = int(input())
-print(bigger(x, y))</t>
+print(maximum(x, y))</t>
         </is>
       </c>
     </row>
@@ -1052,13 +1087,15 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Write a function that returns 'Even' if a number is even and 'Odd' otherwise. Read a number and print the result.
+          <t>In Ravi's hostel, rooms with even numbers are on the left side of the corridor and odd-numbered rooms are on the right. The warden wants a small program to tell which side a room is on. Write a function that takes a number and returns `Even` if the number is even and `Odd` otherwise. Read a number from input, call your function, and print the result.
 ### Input Format
 - Line 1: A number
 ### Output Format
 ```
 Even
 ```
+### Example Walkthrough
+For the sample input, the number is 4. Dividing 4 by 2 leaves no remainder (`4 % 2` is 0), so the function returns `Even` and the program prints `Even`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1181,6 +1218,14 @@
           <t>Even</t>
         </is>
       </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>def even_or_odd(n):
+    # write your code here
+    pass
+print(even_or_odd(int(input())))</t>
+        </is>
+      </c>
       <c r="AG5" t="inlineStr">
         <is>
           <t>def even_or_odd(n):
@@ -1197,7 +1242,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Write a function greet(name, title='Friend') that returns 'Hello &lt;title&gt; &lt;name&gt;'. Read a name and a title; if the title line is empty, rely on the default. Print the greeting.
+          <t>At the college fest registration desk, every guest gets a badge with a friendly greeting. Some guests mention a title like Dr or Prof, while others give no title at all, and those guests should simply be greeted as `Friend`. Write a function `greet(name, title='Friend')` that returns `Hello &lt;title&gt; &lt;name&gt;`. Read a name and a title from input; if the title line is empty, rely on the default value. Print the greeting.
 ### Input Format
 - Line 1: A name
 - Line 2: A title (may be empty or absent)
@@ -1205,6 +1250,8 @@
 ```
 Hello Dr Asha
 ```
+### Example Walkthrough
+For the sample input, the name is `Asha` and the title is `Dr`. Since a title was given, the default is not used, and `greet('Asha', 'Dr')` returns `Hello Dr Asha`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1330,6 +1377,19 @@
       <c r="AE6" t="inlineStr">
         <is>
           <t>Hello Capt Ray</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>def greet(name, title="Friend"):
+    # write your code here
+    pass
+name = input()
+try:
+    title = input()
+except EOFError:
+    title = ""
+print(greet(name, title) if title else greet(name))</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1353,13 +1413,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Write a function that returns the factorial of a number. Read a number and print its factorial.
+          <t>Kiran has won several trophies in inter-college competitions and wonders how many different ways they can be arranged in a row on his shelf. For n trophies, the answer is the factorial of n, which is n x (n-1) x ... x 2 x 1. Write a function named `factorial` that takes a number and returns its factorial. Read a number from input, call your function, and print the result.
 ### Input Format
 - Line 1: A number
 ### Output Format
 ```
 120
 ```
+### Example Walkthrough
+For the sample input, the number is 5. The function computes 5 x 4 x 3 x 2 x 1 = 120, so the program prints `120`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1480,6 +1542,14 @@
       <c r="AE7" t="inlineStr">
         <is>
           <t>6</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>def factorial(n):
+    # write your code here
+    pass
+print(factorial(int(input())))</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1501,13 +1571,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Write a function that returns both the smallest and largest of a list of numbers. Read a line of numbers and print the smallest and largest separated by a space.
+          <t>After the unit test, Professor Iyer wants a quick summary of the class performance: just the lowest and the highest marks. Write a function that takes a list of numbers and returns both the smallest and the largest. Read one line of space-separated numbers, call your function, and print the smallest and largest separated by a space.
 ### Input Format
 - Line 1: Space-separated numbers
 ### Output Format
 ```
 1 5
 ```
+### Example Walkthrough
+For the sample input, the numbers are `3 1 4 1 5`. Scanning through them, the smallest value is 1 and the largest is 5, so the program prints `1 5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1628,6 +1700,16 @@
       <c r="AE8" t="inlineStr">
         <is>
           <t>-100 100</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>def extremes(nums):
+    # write your code here
+    pass
+nums = list(map(int, input().split()))
+low, high = extremes(nums)
+print(low, high)</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1648,13 +1730,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Write a recursive function that returns the factorial of a number (no loops). Read a number and print its factorial.
+          <t>Divya's professor sets a challenge: compute the factorial of a number without using any loop. Instead, the function must call itself, solving a smaller version of the same problem each time, until it reaches 1. Write a recursive function that returns the factorial of a number (no loops allowed). Read a number from input, call your function, and print its factorial.
 ### Input Format
 - Line 1: A number
 ### Output Format
 ```
 120
 ```
+### Example Walkthrough
+For the sample input, the number is 5. The function computes `factorial(5)` as 5 x `factorial(4)`, which becomes 5 x 4 x `factorial(3)`, and so on down to `factorial(1)` = 1, giving 5 x 4 x 3 x 2 x 1 = 120, so the program prints `120`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1775,6 +1859,14 @@
       <c r="AE9" t="inlineStr">
         <is>
           <t>6</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>def factorial(n):
+    # write your code here
+    pass
+print(factorial(int(input())))</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1795,13 +1887,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Write a recursive function that returns the Nth Fibonacci number, where position 0 is 0 and position 1 is 1. Read N and print that Fibonacci number.
+          <t>Members of the college nature club notice that petals on many flowers follow the Fibonacci sequence, where each number is the sum of the two before it: 0, 1, 1, 2, 3, 5, 8, 13, and so on. Write a recursive function that returns the Nth Fibonacci number, where position 0 is 0 and position 1 is 1. Read `N` from input, call your function, and print that Fibonacci number.
 ### Input Format
-- Line 1: N, the position
+- Line 1: `N`, the position
 ### Output Format
 ```
 13
 ```
+### Example Walkthrough
+For the sample input, `N` is 7. Counting the sequence from position 0, we get 0, 1, 1, 2, 3, 5, 8, 13, so position 7 holds 13 and the program prints `13`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1922,6 +2016,14 @@
       <c r="AE10" t="inlineStr">
         <is>
           <t>6765</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>def fib(n):
+    # write your code here
+    pass
+print(fib(int(input())))</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1942,7 +2044,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Write a function make_multiplier(n) that returns a new function which multiplies its argument by n. Read a factor and a value, build the multiplier, and print the result of applying it to the value.
+          <t>A mobile recharge app runs offers like '3x cashback points', and for each offer the app needs a ready-made function that multiplies any points value by that factor. Write a function `make_multiplier(n)` that returns a new function which multiplies its argument by `n`. Read a factor and a value from input, build the multiplier with the factor, apply it to the value, and print the result.
 ### Input Format
 - Line 1: The factor
 - Line 2: The value
@@ -1950,6 +2052,8 @@
 ```
 15
 ```
+### Example Walkthrough
+For the sample input, the factor is 3 and the value is 5. Calling `make_multiplier(3)` returns a new function that triples its input, and applying it to 5 gives 3 x 5 = 15, so the program prints `15`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -2077,6 +2181,17 @@
       <c r="AE11" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>def make_multiplier(n):
+    # write your code here
+    pass
+factor = int(input())
+value = int(input())
+times = make_multiplier(factor)
+print(times(value))</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -2229,6 +2344,14 @@
           <t>Hello, Mohammed!</t>
         </is>
       </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>def greet(name):
+    # write your code here
+    pass
+print(greet(input()))</t>
+        </is>
+      </c>
       <c r="AG12" t="inlineStr">
         <is>
           <t>def greet(name):
@@ -2382,6 +2505,16 @@
           <t>10000</t>
         </is>
       </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>def area(width, height):
+    # write your code here
+    pass
+w = int(input())
+h = int(input())
+print(area(w, h))</t>
+        </is>
+      </c>
       <c r="AG13" t="inlineStr">
         <is>
           <t>def area(width, height):
@@ -2529,6 +2662,14 @@
           <t>1832.0</t>
         </is>
       </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>def to_fahrenheit(c):
+    # write your code here
+    pass
+print(round(to_fahrenheit(float(input())), 1))</t>
+        </is>
+      </c>
       <c r="AG14" t="inlineStr">
         <is>
           <t>def to_fahrenheit(c):
@@ -2674,6 +2815,14 @@
           <t>1000000</t>
         </is>
       </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>def absolute(n):
+    # write your code here
+    pass
+print(absolute(int(input())))</t>
+        </is>
+      </c>
       <c r="AG15" t="inlineStr">
         <is>
           <t>def absolute(n):
@@ -2819,6 +2968,14 @@
           <t>1000</t>
         </is>
       </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>def cube(x):
+    # write your code here
+    pass
+print(cube(int(input())))</t>
+        </is>
+      </c>
       <c r="AG16" t="inlineStr">
         <is>
           <t>def cube(x):
@@ -2964,6 +3121,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>def length(word):
+    # write your code here
+    pass
+print(length(input()))</t>
+        </is>
+      </c>
       <c r="AG17" t="inlineStr">
         <is>
           <t>def length(word):
@@ -3109,6 +3274,15 @@
           <t>600</t>
         </is>
       </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>def total(*args):
+    # write your code here
+    pass
+nums = list(map(int, input().split()))
+print(total(*nums))</t>
+        </is>
+      </c>
       <c r="AG18" t="inlineStr">
         <is>
           <t>def total(*args):
@@ -3253,6 +3427,14 @@
       <c r="AE19" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>def digit_sum(n):
+    # write your code here
+    pass
+print(digit_sum(int(input())))</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -3832,6 +4014,14 @@
           <t>10</t>
         </is>
       </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>def count_vowels(text):
+    # write your code here
+    pass
+print(count_vowels(input()))</t>
+        </is>
+      </c>
       <c r="AG23" t="inlineStr">
         <is>
           <t>def count_vowels(text):
@@ -4126,6 +4316,14 @@
           <t>54</t>
         </is>
       </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>def digit_sum(n):
+    # write your code here
+    pass
+print(digit_sum(abs(int(input()))))</t>
+        </is>
+      </c>
       <c r="AG25" t="inlineStr">
         <is>
           <t>def digit_sum(n):
@@ -4279,6 +4477,16 @@
       <c r="AE26" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>def power(a, b):
+    # write your code here
+    pass
+base = int(input())
+exp = int(input())
+print(power(base, exp))</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -4436,6 +4644,16 @@
       <c r="AE27" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>def gcd(a, b):
+    # write your code here
+    pass
+x = int(input())
+y = int(input())
+print(gcd(x, y))</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -4899,6 +5117,14 @@
           <t>citsiligarfilacrepus</t>
         </is>
       </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>def reverse(s):
+    # write your code here
+    pass
+print(reverse(input()))</t>
+        </is>
+      </c>
       <c r="AG30" t="inlineStr">
         <is>
           <t>def reverse(s):
@@ -5046,6 +5272,14 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>def is_palindrome(s):
+    # write your code here
+    pass
+print("Yes" if is_palindrome(input()) else "No")</t>
+        </is>
+      </c>
       <c r="AG31" t="inlineStr">
         <is>
           <t>def is_palindrome(s):

--- a/content/Question Bank/Coding Questions/Unit 8 - Functions/Unit 8 - Functions - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 8 - Functions/Unit 8 - Functions - Coding Questions.xlsx
@@ -7,7 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH31"/>
+  <dimension ref="A1:AH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -620,12 +623,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -635,7 +648,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>function-definition</t>
+          <t>defining-and-calling-functions</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -778,12 +791,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -793,7 +816,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>parameters-return</t>
+          <t>defining-and-calling-functions</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -945,12 +968,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -960,7 +993,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>parameters-return</t>
+          <t>defining-and-calling-functions</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1061,12 +1094,12 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>def bigger(a, b):
+          <t>def maximum(a, b):
     # write your code here
     pass
 x = int(input())
 y = int(input())
-print(bigger(x, y))</t>
+print(maximum(x, y))</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1111,12 +1144,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1126,7 +1169,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>function-definition</t>
+          <t>defining-and-calling-functions</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1267,12 +1310,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1282,7 +1335,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>parameters-return</t>
+          <t>function-parameters-and-arguments</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1437,12 +1490,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1452,7 +1515,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>function-definition</t>
+          <t>defining-and-calling-functions</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1595,12 +1658,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1610,7 +1683,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>parameters-return</t>
+          <t>defining-and-calling-functions</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1754,12 +1827,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1882,10 +1965,504 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Python - Double Function</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Double Function. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+### Output Format
+```
+4
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>defining-and-calling-functions</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>def double(n): return n*2
+print(double(int(input())))</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Greeting Function</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Greeting Function. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Name
+### Output Format
+```
+Hello Asha
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>function-parameters-and-arguments</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Asha</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Hello Asha</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Rohan</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hello Rohan</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Meena</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hello Meena</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Kabir</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Hello Kabir</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Zoya</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Hello Zoya</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Dev Patel</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hello Dev Patel</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Hello S</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>def greet(name): return "Hello "+name
+print(greet(input()))</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>Python - Recursive Fibonacci</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Members of the college nature club notice that petals on many flowers follow the Fibonacci sequence, where each number is the sum of the two before it: 0, 1, 1, 2, 3, 5, 8, 13, and so on. Write a recursive function that returns the Nth Fibonacci number, where position 0 is 0 and position 1 is 1. Read `N` from input, call your function, and print that Fibonacci number.
 ### Input Format
@@ -1901,124 +2478,134 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>recursion</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>6765</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>def fib(n):
     # write your code here
@@ -2026,7 +2613,7 @@
 print(fib(int(input())))</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>def fib(n):
     if n &lt; 2:
@@ -2036,13 +2623,13 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Multiplier Factory</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>A mobile recharge app runs offers like '3x cashback points', and for each offer the app needs a ready-made function that multiplies any points value by that factor. Write a function `make_multiplier(n)` that returns a new function which multiplies its argument by `n`. Read a factor and a value from input, build the multiplier with the factor, apply it to the value, and print the result.
 ### Input Format
@@ -2059,131 +2646,141 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>function-definition</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>higher-order-functions</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>3
 5</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>10
 10</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>2
 7</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>-3
 4</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>100
 0</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>def make_multiplier(n):
     # write your code here
@@ -2194,7 +2791,7 @@
 print(times(value))</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>def make_multiplier(n):
     def multiply(x):
@@ -2207,13 +2804,13 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Greeting Function</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Write a function that takes a name and returns the greeting 'Hello, &lt;name&gt;!'. Read a name and print the greeting.
 ### Input Format
@@ -2222,129 +2819,141 @@
 ```
 Hello, Asha!
 ```
+### Example Walkthrough
+In the sample, the name is `Asha`. The function returns `Hello, Asha!`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>function-definition</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>defining-and-calling-functions</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O12" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P12" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="b">
-        <v>1</v>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>Asha</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Hello, Asha!</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Kabir</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Hello, Kabir!</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Sam</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Hello, Sam!</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Hello, A!</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Priya</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Hello, Priya!</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>Hello, Z!</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>Mohammed</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>Hello, Mohammed!</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>def greet(name):
     # write your code here
@@ -2352,7 +2961,7 @@
 print(greet(input()))</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>def greet(name):
     return f"Hello, {name}!"
@@ -2360,13 +2969,13 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Rectangle Area</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Write a function that returns the area of a rectangle given its width and height. Read the width and height and print the area.
 ### Input Format
@@ -2376,136 +2985,148 @@
 ```
 12
 ```
+### Example Walkthrough
+In the sample, the width is `3` and the height is `4`. Multiplying them gives `3 x 4 = 12`, so the program prints `12`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>parameters-return</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>defining-and-calling-functions</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O13" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P13" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="b">
-        <v>1</v>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>3
 4</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>5
 5</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>2
 10</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>7
 3</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>100
 100</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>def area(width, height):
     # write your code here
@@ -2515,7 +3136,7 @@
 print(area(w, h))</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>def area(width, height):
     return width * height
@@ -2525,13 +3146,13 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - To Fahrenheit</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Write a function that converts a Celsius temperature to Fahrenheit using F = C * 9 / 5 + 32. Read a Celsius value and print the Fahrenheit value rounded to 1 decimal place.
 ### Input Format
@@ -2540,129 +3161,141 @@
 ```
 32.0
 ```
+### Example Walkthrough
+In the sample, the Celsius value is `0`. Applying the formula gives `0 x 9 / 5 + 32 = 32.0`, so the program prints `32.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>parameters-return</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>defining-and-calling-functions</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O14" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P14" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="b">
-        <v>1</v>
-      </c>
-      <c r="R14" t="inlineStr">
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>32.0</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>212.0</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>98.6</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>-40</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>-40.0</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>-273.15</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>-459.7</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>98.6</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>209.5</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1832.0</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>def to_fahrenheit(c):
     # write your code here
@@ -2670,7 +3303,7 @@
 print(round(to_fahrenheit(float(input())), 1))</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>def to_fahrenheit(c):
     return c * 9 / 5 + 32
@@ -2678,13 +3311,13 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - My Absolute</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Write your own function that returns the absolute value of a number (without using the built-in abs). Read a number and print its absolute value.
 ### Input Format
@@ -2693,129 +3326,141 @@
 ```
 5
 ```
+### Example Walkthrough
+In the sample, the number is `-5`. Its absolute value is `5`, so the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>function-definition</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>defining-and-calling-functions</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O15" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P15" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="b">
-        <v>1</v>
-      </c>
-      <c r="R15" t="inlineStr">
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>-1000000</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1000000</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>1000000</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>1000000</t>
         </is>
       </c>
-      <c r="AF15" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>def absolute(n):
     # write your code here
@@ -2823,7 +3468,7 @@
 print(absolute(int(input())))</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>def absolute(n):
     return -n if n &lt; 0 else n
@@ -2831,13 +3476,13 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Cube It</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Write a function that returns the cube of a number. Read a number and print its cube.
 ### Input Format
@@ -2846,129 +3491,141 @@
 ```
 8
 ```
+### Example Walkthrough
+In the sample, the number is `2`. Cubing it gives `2 x 2 x 2 = 8`, so the program prints `8`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>function-definition</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>defining-and-calling-functions</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O16" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P16" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="b">
-        <v>1</v>
-      </c>
-      <c r="R16" t="inlineStr">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>-125</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="AF16" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>def cube(x):
     # write your code here
@@ -2976,7 +3633,7 @@
 print(cube(int(input())))</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>def cube(x):
     return x * x * x
@@ -2984,13 +3641,13 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Python - Word Length</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Write a function that returns the number of characters in a word. Read a word and print its length using the function.
 ### Input Format
@@ -2999,129 +3656,141 @@
 ```
 5
 ```
+### Example Walkthrough
+In the sample, the word is `hello`. It has `5` characters, so the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>parameters-return</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>defining-and-calling-functions</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O17" t="b">
+      <c r="O9" t="b">
         <v>0</v>
       </c>
-      <c r="P17" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="b">
-        <v>1</v>
-      </c>
-      <c r="R17" t="inlineStr">
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>coding</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>abcdefghij</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>supercalifragilistic</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>def length(word):
     # write your code here
@@ -3129,7 +3798,7 @@
 print(length(input()))</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>def length(word):
     return len(word)
@@ -3137,13 +3806,515 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Area Function</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Area Function. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Width
+- Line 2: Height
+### Output Format
+```
+6
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>function-parameters-and-arguments</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2
+3</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>5
+5</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0
+10</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7
+8</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>-2
+4</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>1
+1</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>100
+2</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>def area(w,h): return w*h
+print(area(int(input()),int(input())))</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Positive Function</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Positive Function. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+### Output Format
+```
+Yes
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>defining-and-calling-functions</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>-99</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>def pos(n): return n&gt;0
+print("Yes" if pos(int(input())) else "No")</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Sum All Arguments</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Write a function that accepts any number of arguments using *args and returns their sum. Read a line of numbers and print their total by unpacking them into the function.
 ### Input Format
@@ -3152,129 +4323,141 @@
 ```
 10
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 3 4`. Adding them gives `10`, so the program prints `10`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>parameters-return</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>function-parameters-and-arguments</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O18" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P18" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="b">
-        <v>1</v>
-      </c>
-      <c r="R18" t="inlineStr">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>10 -5</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>-1 -2 -3</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>100 200 300</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="AF18" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>def total(*args):
     # write your code here
@@ -3283,7 +4466,7 @@
 print(total(*nums))</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>def total(*args):
     return sum(args)
@@ -3292,13 +4475,13 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Digit Sum Function</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Write a function that returns the sum of the digits of a whole number. Read a number and print the digit sum.
 ### Input Format
@@ -3307,129 +4490,141 @@
 ```
 10
 ```
+### Example Walkthrough
+In the sample, the number is `1234`. Its digits `1`, `2`, `3`, and `4` add up to `10`, so the program prints `10`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>function-definition</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>defining-and-calling-functions</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O19" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P19" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q19" t="b">
-        <v>1</v>
-      </c>
-      <c r="R19" t="inlineStr">
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>1234</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>-45</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>999999</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AF19" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>def digit_sum(n):
     # write your code here
@@ -3437,7 +4632,7 @@
 print(digit_sum(int(input())))</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>def digit_sum(n):
     n = abs(n)
@@ -3450,13 +4645,13 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Map to Squares</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Read a line of numbers and use map with a lambda to print each number squared, in order, separated by spaces.
 ### Input Format
@@ -3465,142 +4660,154 @@
 ```
 1 4 9
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 3`. Squaring each gives `1`, `4`, and `9`, so the program prints `1 4 9`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>function-definition</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>higher-order-functions</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O20" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P20" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="b">
-        <v>1</v>
-      </c>
-      <c r="R20" t="inlineStr">
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>1 4 9</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>-2 5</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>4 25</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>-1 -2 -3</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>1 4 9</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1 4 9 16 25 36 49</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>10 -10</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>100 100</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 print(*map(lambda x: x * x, nums))</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Filter Evens</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Read a line of numbers and use filter with a lambda to print only the even numbers, in order, separated by spaces.
 ### Input Format
@@ -3609,137 +4816,149 @@
 ```
 2 4 6
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 3 4 5 6`. The even ones, in order, are `2`, `4`, and `6`, so the program prints `2 4 6`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>function-definition</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>higher-order-functions</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O21" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P21" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="b">
-        <v>1</v>
-      </c>
-      <c r="R21" t="inlineStr">
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>2 4 6</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>10 15 20</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>10 20</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>2 4 6</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>2 4 6</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>1 3 5</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>-2 -4 3</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>-2 -4</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2 4 6 8 10</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 print(*filter(lambda x: x % 2 == 0, nums))</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Sort by Absolute Value</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Read a line of numbers and print them sorted by their absolute value from smallest to largest, using a lambda as the sort key.
 ### Input Format
@@ -3748,142 +4967,154 @@
 ```
 1 -2 -3
 ```
+### Example Walkthrough
+In the sample, the numbers are `-3 1 -2`. Their absolute values are `3`, `1`, and `2`, so sorting from smallest to largest absolute value gives `1`, `-2`, `-3`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>function-definition</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>higher-order-functions</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O22" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P22" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="b">
-        <v>1</v>
-      </c>
-      <c r="R22" t="inlineStr">
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>-3 1 -2</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>1 -2 -3</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>5 -5 2</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>2 5 -5</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>-1 -2 -3</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>-1 -2 -3</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0 -1 1</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>0 -1 1</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>10 -3 -10 3</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>-3 3 10 -10</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 print(*sorted(nums, key=lambda x: abs(x)))</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Count Vowels Function</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Write a function that returns how many vowels are in a piece of text (ignoring case). Read a line and print the vowel count.
 ### Input Format
@@ -3892,129 +5123,141 @@
 ```
 5
 ```
+### Example Walkthrough
+In the sample, the text is `education`. It contains `5` vowels (`e`, `u`, `a`, `i`, `o`), so the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>function-definition</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>defining-and-calling-functions</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O23" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P23" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q23" t="b">
-        <v>1</v>
-      </c>
-      <c r="R23" t="inlineStr">
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>education</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>xyz</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>AEIOU</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>bcdfg</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>The Quick Brown Fox</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>aaaaaaaaaa</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AF23" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>def count_vowels(text):
     # write your code here
@@ -4022,7 +5265,7 @@
 print(count_vowels(input()))</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>def count_vowels(text):
     count = 0
@@ -4034,13 +5277,13 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Product with Reduce</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Read a line of numbers and use functools.reduce with a lambda to print the product of all of them.
 ### Input Format
@@ -4049,129 +5292,141 @@
 ```
 24
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 3 4`. Multiplying them together gives `1 x 2 x 3 x 4 = 24`, so the program prints `24`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>function-definition</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>higher-order-functions</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O24" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P24" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="b">
-        <v>1</v>
-      </c>
-      <c r="R24" t="inlineStr">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>2 2 2</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>0 5 6</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>-1 2 -3</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="AG24" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>from functools import reduce
 nums = list(map(int, input().split()))
@@ -4179,13 +5434,661 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - Flexible Sum</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Flexible Sum. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Integers
+### Output Format
+```
+6
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>function-parameters-and-arguments</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1 2 3</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0 -1 1</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>10 20</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>100 200 300</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>-5 -5</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>def add_all(*nums): return sum(nums)
+nums=[int(x) for x in input().split()]
+print(add_all(*nums))</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Lambda Sort</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Lambda Sort. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Words
+### Output Format
+```
+b aa ccc
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>lambda-functions</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>aa b ccc</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>b aa ccc</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>python java c</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>c java python</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>same size</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>same size</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>a ab abc abcd</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>a ab abc abcd</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>zz yyy xx</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>zz xx yyy</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>red blue green</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>red blue green</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>words=input().split(); words.sort(key=lambda w:len(w)); print(*words)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Map Cubes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Map Cubes. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Integers
+### Output Format
+```
+1 8 27
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>higher-order-functions</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1 2 3</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1 8 27</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>-1 2</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-1 8</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10 0</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1000 0</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2 4</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>8 64</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>-2 -3</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>-8 -27</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>def cube(n): return n**3
+print(*map(cube, map(int,input().split())))</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Recursive Digit Sum</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Write a recursive function that returns the sum of the digits of a whole number (no loops). Read a number and print the digit sum.
 ### Input Format
@@ -4194,129 +6097,141 @@
 ```
 10
 ```
+### Example Walkthrough
+In the sample, the number is `1234`. Its digits sum to `1 + 2 + 3 + 4 = 10`, so the program prints `10`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>recursion</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O25" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P25" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q25" t="b">
-        <v>1</v>
-      </c>
-      <c r="R25" t="inlineStr">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>1234</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>9999</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>-45</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>999999</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="AF25" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>def digit_sum(n):
     # write your code here
@@ -4324,7 +6239,7 @@
 print(digit_sum(abs(int(input()))))</t>
         </is>
       </c>
-      <c r="AG25" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>def digit_sum(n):
     if n &lt; 10:
@@ -4334,13 +6249,13 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Recursive Power</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Write a recursive function that returns a raised to the power b (b is a non-negative whole number). Read a and b and print a to the power b.
 ### Input Format
@@ -4350,136 +6265,148 @@
 ```
 1024
 ```
+### Example Walkthrough
+In the sample, `a` is `2` and `b` is `10`. Computing `2` raised to the power `10` gives `1024`, so the program prints `1024`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>recursion</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O26" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P26" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="b">
-        <v>1</v>
-      </c>
-      <c r="R26" t="inlineStr">
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>2
 10</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>5
 0</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>3
 4</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>1
 5</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>-2
 3</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>10
 0</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AF26" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>def power(a, b):
     # write your code here
@@ -4489,7 +6416,7 @@
 print(power(base, exp))</t>
         </is>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>def power(a, b):
     if b == 0:
@@ -4501,13 +6428,13 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Recursive GCD</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Write a recursive function that returns the greatest common divisor of two numbers. Read two numbers and print their GCD.
 ### Input Format
@@ -4517,136 +6444,148 @@
 ```
 6
 ```
+### Example Walkthrough
+In the sample, the numbers are `12` and `18`. Their greatest common divisor is `6`, so the program prints `6`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>recursion</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O27" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P27" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="b">
-        <v>1</v>
-      </c>
-      <c r="R27" t="inlineStr">
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>12
 18</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>17
 5</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>100
 25</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>7
 7</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>1000
 999</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AF27" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>def gcd(a, b):
     # write your code here
@@ -4656,7 +6595,7 @@
 print(gcd(x, y))</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>def gcd(a, b):
     if b == 0:
@@ -4668,13 +6607,13 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Mini Calculator</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Store the operations +, -, and * in a dictionary of lambdas. Read a number, an operator, and a second number, then print the result by looking up the operator.
 ### Input Format
@@ -4685,143 +6624,155 @@
 ```
 10
 ```
+### Example Walkthrough
+In the sample, the numbers are `6` and `4` with the operator `+`. Looking up `+` in the dictionary and applying it gives `6 + 4 = 10`, so the program prints `10`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>function-definition</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>lambda-functions</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O28" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P28" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q28" t="b">
-        <v>1</v>
-      </c>
-      <c r="R28" t="inlineStr">
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>6
 +
 4</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>10
 -
 3</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>5
 *
 6</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>0
 +
 0</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>-5
 -
 -3</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>1
 *
 1</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>100
 +
 200</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>ops = {
     "+": lambda x, y: x + y,
@@ -4835,13 +6786,13 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Sum of Even Squares</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Read a line of numbers. Using filter to keep the even numbers and map to square them, print the sum of the squares of the even numbers.
 ### Input Format
@@ -4850,129 +6801,141 @@
 ```
 20
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 3 4`. The even numbers are `2` and `4`, whose squares are `4` and `16`, summing to `20`, so the program prints `20`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>function-definition</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>higher-order-functions</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O29" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q29" t="b">
-        <v>1</v>
-      </c>
-      <c r="R29" t="inlineStr">
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>2 4 6</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1 3 5</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>-2 -4 3</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>10 -10 5</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 evens = filter(lambda x: x % 2 == 0, nums)
@@ -4980,13 +6943,13 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Recursive String Reverse</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Write a recursive function that returns a string reversed (no loops and no slicing tricks other than peeling one character at a time). Read a word and print it reversed.
 ### Input Format
@@ -4995,129 +6958,141 @@
 ```
 olleh
 ```
+### Example Walkthrough
+In the sample, the word is `hello`. Reversing it one character at a time gives `olleh`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>recursion</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O30" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P30" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q30" t="b">
-        <v>1</v>
-      </c>
-      <c r="R30" t="inlineStr">
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>olleh</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>abcde</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>edcba</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>ab</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>ba</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>racecar</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>racecar</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>supercalifragilistic</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>citsiligarfilacrepus</t>
         </is>
       </c>
-      <c r="AF30" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>def reverse(s):
     # write your code here
@@ -5125,7 +7100,7 @@
 print(reverse(input()))</t>
         </is>
       </c>
-      <c r="AG30" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>def reverse(s):
     if len(s) &lt;= 1:
@@ -5135,13 +7110,13 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Recursive Palindrome</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Write a recursive function that returns whether a word is a palindrome. Read a word and print 'Yes' if it is a palindrome, otherwise 'No'.
 ### Input Format
@@ -5150,129 +7125,141 @@
 ```
 Yes
 ```
+### Example Walkthrough
+In the sample, the word is `racecar`. Since it reads the same forwards and backwards, the program prints `Yes`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>recursion</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O31" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q31" t="b">
-        <v>1</v>
-      </c>
-      <c r="R31" t="inlineStr">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>racecar</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>ab</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>noon</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>abcba</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AF31" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>def is_palindrome(s):
     # write your code here
@@ -5280,7 +7267,7 @@
 print("Yes" if is_palindrome(input()) else "No")</t>
         </is>
       </c>
-      <c r="AG31" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>def is_palindrome(s):
     if len(s) &lt;= 1:
@@ -5290,6 +7277,484 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - Recursive Sum</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Recursive Sum. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+### Output Format
+```
+15
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>recursion</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>5050</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>def total(n): return 0 if n&lt;=0 else n+total(n-1)
+print(total(int(input())))</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Scoped Counter</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Scoped Counter. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+### Output Format
+```
+3
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>variable-scope-and-legb</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>def make_counter():
+ count=0
+ def inc():
+  nonlocal count; count+=1; return count
+ return inc
+n=int(input()); c=make_counter(); last=0
+for _ in range(n): last=c()
+print(last)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Documented Power</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Documented Power. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Base
+- Line 2: Exponent
+### Output Format
+```
+8
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>docstrings-and-clean-code</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2
+3</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>5
+0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>10
+2</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>-2
+3</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>3
+4</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0
+5</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>1
+99</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>def power(base, exponent):
+ """Return base raised to exponent."""
+ return base**exponent
+print(power(int(input()),int(input())))</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content/Question Bank/Coding Questions/Unit 8 - Functions/Unit 8 - Functions - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 8 - Functions/Unit 8 - Functions - Coding Questions.xlsx
@@ -1970,16 +1970,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Double Function. Read the input values and print the required result exactly.
+          <t>A coupon app doubles the loyalty points a customer earns during a special promotion weekend, using a small reusable function so the doubling logic lives in one place.
+Write a function `double(n)` that returns twice the value of `n`. Read a whole number and print the result of calling `double` on it.
 ### Input Format
-- Line 1: N
+- Line 1: A whole number
 ### Output Format
 ```
 4
 ```
+### Example Walkthrough
+In the sample, the number is 2. Calling `double(2)` returns 4, so the program prints `4`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2124,16 +2127,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Greeting Function. Read the input values and print the required result exactly.
+          <t>A campus kiosk's touchscreen greets each visitor by name the moment they scan their ID card, using a reusable function so the greeting logic is defined only once.
+Write a function `greet(name)` that returns the string `"Hello "` followed by the name (a single space, no punctuation). Read a name and print the result of calling `greet` on it.
 ### Input Format
-- Line 1: Name
+- Line 1: A name
 ### Output Format
 ```
 Hello Asha
 ```
+### Example Walkthrough
+In the sample, the name is `Asha`. Calling `greet("Asha")` returns `"Hello Asha"`, which the program prints.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The input is a valid name with no leading or trailing spaces.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3814,7 +3820,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Area Function. Read the input values and print the required result exactly.
+          <t>A flooring calculator app computes the area of a rectangular room from its width and height, in a reusable function so the same calculation can be reused for any room in the house.
+Write a function `area(w, h)` that returns the product of `w` and `h`. Read the width and height as two whole numbers and print the result of calling `area` on them.
 ### Input Format
 - Line 1: Width
 - Line 2: Height
@@ -3822,9 +3829,11 @@
 ```
 6
 ```
+### Example Walkthrough
+In the sample, the width is 2 and the height is 3. Calling `area(2, 3)` returns 6, so the program prints `6`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -3976,16 +3985,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Positive Function. Read the input values and print the required result exactly.
+          <t>A budgeting app flags whether a transaction amount is a credit or not, using a small function that answers the yes/no question so the check can be reused across the whole app.
+Write a function `pos(n)` that returns `True` if `n` is strictly greater than 0, and `False` otherwise. Read a whole number and print `Yes` if calling `pos` on it returns `True`, and `No` otherwise.
 ### Input Format
-- Line 1: N
+- Line 1: A whole number
 ### Output Format
 ```
 Yes
 ```
+### Example Walkthrough
+In the sample, the number is 1. Calling `pos(1)` returns `True` since 1 is greater than 0, so the program prints `Yes`. A value of 0 would return `False` and print `No`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -5442,16 +5454,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Flexible Sum. Read the input values and print the required result exactly.
+          <t>A donation tracker needs to add up any number of pledged amounts entered on one line, since different fundraising events may have a different number of donors and the code shouldn't need to change for each event.
+Write a function `add_all` that accepts any number of arguments using `*args` and returns their sum. Read a line of space-separated whole numbers, pass them all to `add_all`, and print the result.
 ### Input Format
-- Line 1: Integers
+- Line 1: Space-separated whole numbers
 ### Output Format
 ```
 6
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 3`. Calling `add_all(1, 2, 3)` returns 6, so the program prints `6`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -5597,16 +5612,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Lambda Sort. Read the input values and print the required result exactly.
+          <t>A word-game app arranges the words a player types from shortest to longest to build a word ladder, using a lambda as the sort key instead of writing a separate function. Words of the same length keep their original order.
+Write a program that reads a line of space-separated words and prints them sorted from shortest to longest (by number of characters), separated by single spaces, using `sort` with a `lambda` key.
 ### Input Format
-- Line 1: Words
+- Line 1: Space-separated words
 ### Output Format
 ```
 b aa ccc
 ```
+### Example Walkthrough
+In the sample, the words are `aa b ccc` with lengths 2, 1, and 3. Sorting by length gives `b` (length 1), `aa` (length 2), `ccc` (length 3), so the program prints `b aa ccc`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The input is a valid line of space-separated words.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -5750,16 +5768,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Map Cubes. Read the input values and print the required result exactly.
+          <t>A math visualizer computes the cube of every number a student enters to plot how fast values grow, applying a `cube` function to the whole list at once using Python's `map`.
+Write a function `cube(n)` that returns `n` raised to the power 3. Read a line of space-separated whole numbers, use `map` to apply `cube` to each one, and print the results separated by single spaces.
 ### Input Format
-- Line 1: Integers
+- Line 1: Space-separated whole numbers
 ### Output Format
 ```
 1 8 27
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 3`. Cubing each gives 1, 8, and 27, so the program prints `1 8 27`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -7285,16 +7306,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Recursive Sum. Read the input values and print the required result exactly.
+          <t>A staircase-climbing app calculates the total step count by adding every step number from 1 up to N, but the developer wants practice with recursion, so the function calls itself with a smaller N each time instead of using a loop.
+Write a function `total(n)` that returns 0 if `n` is 0 or less, and otherwise returns `n` plus the result of calling `total(n - 1)`. Read a whole number and print the result of calling `total` on it.
 ### Input Format
 - Line 1: N
 ### Output Format
 ```
 15
 ```
+### Example Walkthrough
+In the sample, N is 5. `total(5)` calls `5 + total(4)`, which calls `4 + total(3)`, and so on down to `total(0)` which returns 0; adding everything back up gives 5+4+3+2+1 = 15, so the program prints `15`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -7439,16 +7463,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Scoped Counter. Read the input values and print the required result exactly.
+          <t>A gym turnstile counts each entry using a counter that is set up once when the gym opens. Every time someone taps in, an inner function increments a count that only it can access, thanks to closures and the `nonlocal` keyword, and the front desk display shows the count after the most recent tap.
+Write a function `make_counter()` that creates a local variable `count` starting at 0 and returns an inner function `inc` which increments `count` (using `nonlocal`) and returns the new value. Read a whole number N, call the returned `inc` function N times, and print the value returned by the last call.
 ### Input Format
-- Line 1: N
+- Line 1: N, the number of taps
 ### Output Format
 ```
 3
 ```
+### Example Walkthrough
+In the sample, N is 3. Calling the counter's `inc` function three times increments the hidden count from 0 to 1, then 2, then 3, so the last call returns 3 and the program prints `3`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -7599,7 +7626,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Documented Power. Read the input values and print the required result exactly.
+          <t>A scientific calculator app exposes a `power` function with a clear docstring explaining what it does, so other developers can call `help(power)` to learn its behavior without reading the implementation. The function raises a base number to an exponent.
+Write a function `power(base, exponent)` with a docstring describing that it returns `base` raised to `exponent`, and have it return `base ** exponent`. Read the base and the exponent as two whole numbers and print the result of calling `power` on them.
 ### Input Format
 - Line 1: Base
 - Line 2: Exponent
@@ -7607,9 +7635,11 @@
 ```
 8
 ```
+### Example Walkthrough
+In the sample, the base is 2 and the exponent is 3. Calling `power(2, 3)` returns 2 to the power of 3, which is 8, so the program prints `8`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">

--- a/content/Question Bank/Coding Questions/Unit 8 - Functions/Unit 8 - Functions - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 8 - Functions/Unit 8 - Functions - Coding Questions.xlsx
@@ -7,10 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - Coding - Unit 8" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH11"/>
+  <dimension ref="A1:AH41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,17 +597,11 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>Meena is helping her father lay tiles in their square courtyard in Mysuru. If one side needs a certain number of tiles, the total number of tiles is that number multiplied by itself. Write a function named `square` that takes one number and returns its square. Then read a number from input, call your function, and print the result.
-### Input Format
-- Line 1: A number
-### Output Format
-```
-25
-```
 ### Example Walkthrough
 For the sample input, the number read is 5. The function multiplies 5 by itself, giving 5 x 5 = 25, so the program prints `25`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -752,9 +743,10 @@
       <c r="AG2" t="inlineStr">
         <is>
           <t>def square(x):
+    # Multiplying a number by itself gives its square
     return x * x
-n = int(input())
-print(square(n))</t>
+n = int(input())      # read the number typed by the user
+print(square(n))      # call the function and print the result</t>
         </is>
       </c>
     </row>
@@ -767,18 +759,11 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>Arjun buys a samosa and a cup of tea at the college canteen, and the cashier quickly adds the two prices to tell him the bill. Write a function named `add` that takes two numbers and returns their sum. Read two numbers from input, call your function, and print the total.
-### Input Format
-- Line 1: First number
-- Line 2: Second number
-### Output Format
-```
-7
-```
 ### Example Walkthrough
 For the sample input, the two numbers are 3 and 4. The function returns 3 + 4 = 7, so the program prints `7`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -928,10 +913,11 @@
       <c r="AG3" t="inlineStr">
         <is>
           <t>def add(a, b):
+    # Adding two numbers together gives their sum
     return a + b
-x = int(input())
-y = int(input())
-print(add(x, y))</t>
+x = int(input())      # first price
+y = int(input())      # second price
+print(add(x, y))      # call the function and print the total</t>
         </is>
       </c>
     </row>
@@ -944,18 +930,11 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>Priya and Rahul compare their marks after the weekly Python quiz, and their teacher announces only the higher score. Write a function named `maximum` that takes two numbers and returns the larger one. Read two numbers from input, call your function, and print the larger number.
-### Input Format
-- Line 1: First number
-- Line 2: Second number
-### Output Format
-```
-9
-```
 ### Example Walkthrough
 For the sample input, the two numbers are 3 and 9. Since 9 is greater than 3, the function returns `9` and the program prints `9`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1105,10 +1084,11 @@
       <c r="AG4" t="inlineStr">
         <is>
           <t>def maximum(a, b):
+    # Compare the two values and return the larger one
     return a if a &gt;= b else b
-x = int(input())
-y = int(input())
-print(maximum(x, y))</t>
+x = int(input())      # first score
+y = int(input())      # second score
+print(maximum(x, y))  # print whichever score is larger</t>
         </is>
       </c>
     </row>
@@ -1121,17 +1101,11 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>In Ravi's hostel, rooms with even numbers are on the left side of the corridor and odd-numbered rooms are on the right. The warden wants a small program to tell which side a room is on. Write a function that takes a number and returns `Even` if the number is even and `Odd` otherwise. Read a number from input, call your function, and print the result.
-### Input Format
-- Line 1: A number
-### Output Format
-```
-Even
-```
 ### Example Walkthrough
 For the sample input, the number is 4. Dividing 4 by 2 leaves no remainder (`4 % 2` is 0), so the function returns `Even` and the program prints `Even`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1272,8 +1246,9 @@
       <c r="AG5" t="inlineStr">
         <is>
           <t>def even_or_odd(n):
+    # A number is even if it divides by 2 with no remainder
     return "Even" if n % 2 == 0 else "Odd"
-print(even_or_odd(int(input())))</t>
+print(even_or_odd(int(input())))  # read a number and print which side it's on</t>
         </is>
       </c>
     </row>
@@ -1286,18 +1261,11 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>At the college fest registration desk, every guest gets a badge with a friendly greeting. Some guests mention a title like Dr or Prof, while others give no title at all, and those guests should simply be greeted as `Friend`. Write a function `greet(name, title='Friend')` that returns `Hello &lt;title&gt; &lt;name&gt;`. Read a name and a title from input; if the title line is empty, rely on the default value. Print the greeting.
-### Input Format
-- Line 1: A name
-- Line 2: A title (may be empty or absent)
-### Output Format
-```
-Hello Dr Asha
-```
 ### Example Walkthrough
 For the sample input, the name is `Asha` and the title is `Dr`. Since a title was given, the default is not used, and `greet('Asha', 'Dr')` returns `Hello Dr Asha`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1448,13 +1416,14 @@
       <c r="AG6" t="inlineStr">
         <is>
           <t>def greet(name, title="Friend"):
+    # title has a default value, used when the caller doesn't pass one
     return f"Hello {title} {name}"
-name = input()
+name = input()          # guest's name is always given
 try:
-    title = input()
+    title = input()      # title is optional, may not be provided
 except EOFError:
-    title = ""
-print(greet(name, title) if title else greet(name))</t>
+    title = ""            # no second line means no title was given
+print(greet(name, title) if title else greet(name))  # use default title if none given</t>
         </is>
       </c>
     </row>
@@ -1467,17 +1436,11 @@
       <c r="B7" t="inlineStr">
         <is>
           <t>Kiran has won several trophies in inter-college competitions and wonders how many different ways they can be arranged in a row on his shelf. For n trophies, the answer is the factorial of n, which is n x (n-1) x ... x 2 x 1. Write a function named `factorial` that takes a number and returns its factorial. Read a number from input, call your function, and print the result.
-### Input Format
-- Line 1: A number
-### Output Format
-```
-120
-```
 ### Example Walkthrough
 For the sample input, the number is 5. The function computes 5 x 4 x 3 x 2 x 1 = 120, so the program prints `120`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1619,7 +1582,7 @@
         <is>
           <t>def factorial(n):
     result = 1
-    for i in range(2, n + 1):
+    for i in range(2, n + 1):   # multiply every number from 2 up to n
         result *= i
     return result
 print(factorial(int(input())))</t>
@@ -1635,17 +1598,11 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>After the unit test, Professor Iyer wants a quick summary of the class performance: just the lowest and the highest marks. Write a function that takes a list of numbers and returns both the smallest and the largest. Read one line of space-separated numbers, call your function, and print the smallest and largest separated by a space.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-1 5
-```
 ### Example Walkthrough
 For the sample input, the numbers are `3 1 4 1 5`. Scanning through them, the smallest value is 1 and the largest is 5, so the program prints `1 5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1788,9 +1745,10 @@
       <c r="AG8" t="inlineStr">
         <is>
           <t>def extremes(nums):
+    # Return both the smallest and largest value as a tuple
     return min(nums), max(nums)
-nums = list(map(int, input().split()))
-low, high = extremes(nums)
+nums = list(map(int, input().split()))  # read all marks on one line
+low, high = extremes(nums)               # unpack the returned tuple
 print(low, high)</t>
         </is>
       </c>
@@ -1804,17 +1762,11 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>Divya's professor sets a challenge: compute the factorial of a number without using any loop. Instead, the function must call itself, solving a smaller version of the same problem each time, until it reaches 1. Write a recursive function that returns the factorial of a number (no loops allowed). Read a number from input, call your function, and print its factorial.
-### Input Format
-- Line 1: A number
-### Output Format
-```
-120
-```
 ### Example Walkthrough
 For the sample input, the number is 5. The function computes `factorial(5)` as 5 x `factorial(4)`, which becomes 5 x 4 x `factorial(3)`, and so on down to `factorial(1)` = 1, giving 5 x 4 x 3 x 2 x 1 = 120, so the program prints `120`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1955,8 +1907,10 @@
       <c r="AG9" t="inlineStr">
         <is>
           <t>def factorial(n):
+    # Base case: factorial of 0 or 1 is defined directly
     if n &lt;= 1:
         return 1
+    # Recursive case: n! = n times factorial of (n - 1)
     return n * factorial(n - 1)
 print(factorial(int(input())))</t>
         </is>
@@ -1972,17 +1926,11 @@
         <is>
           <t>A coupon app doubles the loyalty points a customer earns during a special promotion weekend, using a small reusable function so the doubling logic lives in one place.
 Write a function `double(n)` that returns twice the value of `n`. Read a whole number and print the result of calling `double` on it.
-### Input Format
-- Line 1: A whole number
-### Output Format
-```
-4
-```
 ### Example Walkthrough
 In the sample, the number is 2. Calling `double(2)` returns 4, so the program prints `4`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2114,7 +2062,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>def double(n): return n*2
+          <t>def double(n): return n*2  # doubling logic lives in one reusable place
 print(double(int(input())))</t>
         </is>
       </c>
@@ -2129,17 +2077,11 @@
         <is>
           <t>A campus kiosk's touchscreen greets each visitor by name the moment they scan their ID card, using a reusable function so the greeting logic is defined only once.
 Write a function `greet(name)` that returns the string `"Hello "` followed by the name (a single space, no punctuation). Read a name and print the result of calling `greet` on it.
-### Input Format
-- Line 1: A name
-### Output Format
-```
-Hello Asha
-```
 ### Example Walkthrough
 In the sample, the name is `Asha`. Calling `greet("Asha")` returns `"Hello Asha"`, which the program prints.
 ### Constraints
 - The input is a valid name with no leading or trailing spaces.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2271,347 +2213,155 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>def greet(name): return "Hello "+name
+          <t>def greet(name): return "Hello "+name  # build the greeting string
 print(greet(input()))</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Python - Recursive Fibonacci</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Members of the college nature club notice that petals on many flowers follow the Fibonacci sequence, where each number is the sum of the two before it: 0, 1, 1, 2, 3, 5, 8, 13, and so on. Write a recursive function that returns the Nth Fibonacci number, where position 0 is 0 and position 1 is 1. Read `N` from input, call your function, and print that Fibonacci number.
-### Input Format
-- Line 1: `N`, the position
-### Output Format
-```
-13
-```
 ### Example Walkthrough
 For the sample input, `N` is 7. Counting the sequence from position 0, we get 0, 1, 1, 2, 3, 5, 8, 13, so position 7 holds 13 and the program prints `13`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>recursion</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O12" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>6765</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>def fib(n):
     # write your code here
@@ -2619,174 +2369,169 @@
 print(fib(int(input())))</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG12" t="inlineStr">
         <is>
           <t>def fib(n):
+    # Base case: the first two Fibonacci numbers are defined directly
     if n &lt; 2:
         return n
+    # Recursive case: each number is the sum of the two before it
     return fib(n - 1) + fib(n - 2)
 print(fib(int(input())))</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Python - Multiplier Factory</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>A mobile recharge app runs offers like '3x cashback points', and for each offer the app needs a ready-made function that multiplies any points value by that factor. Write a function `make_multiplier(n)` that returns a new function which multiplies its argument by `n`. Read a factor and a value from input, build the multiplier with the factor, apply it to the value, and print the result.
-### Input Format
-- Line 1: The factor
-- Line 2: The value
-### Output Format
-```
-15
-```
 ### Example Walkthrough
 For the sample input, the factor is 3 and the value is 5. Calling `make_multiplier(3)` returns a new function that triples its input, and applying it to 5 gives 3 x 5 = 15, so the program prints `15`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>higher-order-functions</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O13" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>3
 5</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>10
 10</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>2
 7</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>-3
 4</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>100
 0</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AF13" t="inlineStr">
         <is>
           <t>def make_multiplier(n):
     # write your code here
@@ -2797,12 +2542,12 @@
 print(times(value))</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG13" t="inlineStr">
         <is>
           <t>def make_multiplier(n):
     def multiply(x):
-        return n * x
-    return multiply
+        return n * x     # inner function "remembers" n from the enclosing scope
+    return multiply       # closure: returning a function that carries its own state
 factor = int(input())
 value = int(input())
 times = make_multiplier(factor)
@@ -2810,156 +2555,151 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Python - Greeting Function</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Write a function that takes a name and returns the greeting 'Hello, &lt;name&gt;!'. Read a name and print the greeting.
-### Input Format
-- Line 1: A name
-### Output Format
-```
-Hello, Asha!
-```
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Python - Welcome Banner</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>A library's self-checkout kiosk displays a personalized welcome banner the moment a member scans their card. The wording lives in one reusable function so the greeting only has to be written once.
+Write a function `greet(name)` that returns the string `Hello, &lt;name&gt;!`. Read a name and print the greeting.
 ### Example Walkthrough
 In the sample, the name is `Asha`. The function returns `Hello, Asha!`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>defining-and-calling-functions</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O14" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>Asha</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>Hello, Asha!</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Kabir</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Hello, Kabir!</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Sam</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Hello, Sam!</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>Hello, A!</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>Priya</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>Hello, Priya!</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>Hello, Z!</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>Mohammed</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>Hello, Mohammed!</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AF14" t="inlineStr">
         <is>
           <t>def greet(name):
     # write your code here
@@ -2967,172 +2707,167 @@
 print(greet(input()))</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG14" t="inlineStr">
         <is>
           <t>def greet(name):
+    # f-string builds the banner text with the member's name inside
     return f"Hello, {name}!"
 print(greet(input()))</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Python - Rectangle Area</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Write a function that returns the area of a rectangle given its width and height. Read the width and height and print the area.
-### Input Format
-- Line 1: Width
-- Line 2: Height
-### Output Format
-```
-12
-```
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Python - Tile Flooring Calculator</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>A home-renovation app estimates how many square feet of flooring a rectangular room needs before the installer orders tiles. The width and height of the room are entered separately, and a single reusable function computes the area so the same calculation works for every room in the house.
+Write a function `area(width, height)` that returns the room's area. Read the width and height and print the area using the function.
 ### Example Walkthrough
 In the sample, the width is `3` and the height is `4`. Multiplying them gives `3 x 4 = 12`, so the program prints `12`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>defining-and-calling-functions</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O15" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>3
 4</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>5
 5</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>2
 10</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>7
 3</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>100
 100</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AF15" t="inlineStr">
         <is>
           <t>def area(width, height):
     # write your code here
@@ -3142,166 +2877,162 @@
 print(area(w, h))</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>def area(width, height):
+    # Area of a rectangle is width times height
     return width * height
-w = int(input())
-h = int(input())
+w = int(input())      # room width
+h = int(input())      # room height
 print(area(w, h))</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Python - To Fahrenheit</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Write a function that converts a Celsius temperature to Fahrenheit using F = C * 9 / 5 + 32. Read a Celsius value and print the Fahrenheit value rounded to 1 decimal place.
-### Input Format
-- Line 1: Temperature in Celsius
-### Output Format
-```
-32.0
-```
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Python - Cold Storage Temperature Converter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A cold-storage warehouse's sensors report temperatures in Celsius, but the logistics partner's dashboard only understands Fahrenheit. The warehouse system needs one reusable function that converts every Celsius reading before it is sent over.
+Write a function `to_fahrenheit(c)` that converts a Celsius temperature to Fahrenheit using F = C * 9 / 5 + 32. Read a Celsius value and print the Fahrenheit value rounded to 1 decimal place.
 ### Example Walkthrough
 In the sample, the Celsius value is `0`. Applying the formula gives `0 x 9 / 5 + 32 = 32.0`, so the program prints `32.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>defining-and-calling-functions</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O16" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>32.0</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>212.0</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>98.6</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>-40</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>-40.0</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>-273.15</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>-459.7</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>98.6</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>209.5</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>1832.0</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AF16" t="inlineStr">
         <is>
           <t>def to_fahrenheit(c):
     # write your code here
@@ -3309,164 +3040,159 @@
 print(round(to_fahrenheit(float(input())), 1))</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG16" t="inlineStr">
         <is>
           <t>def to_fahrenheit(c):
+    # Standard Celsius-to-Fahrenheit conversion formula
     return c * 9 / 5 + 32
-print(round(to_fahrenheit(float(input())), 1))</t>
+print(round(to_fahrenheit(float(input())), 1))  # round to 1 decimal place</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Python - My Absolute</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Write your own function that returns the absolute value of a number (without using the built-in abs). Read a number and print its absolute value.
-### Input Format
-- Line 1: A number
-### Output Format
-```
-5
-```
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A fitness app tracks how far a user's daily step count strays from their goal, whether they fall short or go over it, and the dashboard needs to display that gap as a plain positive number either way. Write your own function that returns the absolute value of a number (without using the built-in abs). Read a number and print its absolute value.
 ### Example Walkthrough
 In the sample, the number is `-5`. Its absolute value is `5`, so the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>defining-and-calling-functions</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O17" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>-1000000</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>1000000</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>1000000</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>1000000</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AF17" t="inlineStr">
         <is>
           <t>def absolute(n):
     # write your code here
@@ -3474,164 +3200,160 @@
 print(absolute(int(input())))</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG17" t="inlineStr">
         <is>
           <t>def absolute(n):
+    # Flip the sign only if the number is negative
     return -n if n &lt; 0 else n
 print(absolute(int(input())))</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Python - Cube It</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Write a function that returns the cube of a number. Read a number and print its cube.
-### Input Format
-- Line 1: A number
-### Output Format
-```
-8
-```
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Python - Number Cubed Checker</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A math-practice app for middle schoolers lets a student type any number and instantly see it cubed, so they can notice the pattern that cubing a negative number gives a negative result.
+Write a function `cube(x)` that returns the cube of a number. Read a number and print its cube using the function.
 ### Example Walkthrough
 In the sample, the number is `2`. Cubing it gives `2 x 2 x 2 = 8`, so the program prints `8`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>defining-and-calling-functions</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O18" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>-125</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AF18" t="inlineStr">
         <is>
           <t>def cube(x):
     # write your code here
@@ -3639,164 +3361,160 @@
 print(cube(int(input())))</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG18" t="inlineStr">
         <is>
           <t>def cube(x):
+    # Multiplying a number by itself three times gives its cube
     return x * x * x
 print(cube(int(input())))</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Python - Word Length</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Write a function that returns the number of characters in a word. Read a word and print its length using the function.
-### Input Format
-- Line 1: A word
-### Output Format
-```
-5
-```
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Python - Username Length Checker</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A social app enforces a character limit on usernames and needs a single reusable function to measure how many characters a proposed username has before accepting it.
+Write a function `length(word)` that returns the number of characters in a word. Read a word and print its length using the function.
 ### Example Walkthrough
 In the sample, the word is `hello`. It has `5` characters, so the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>defining-and-calling-functions</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O19" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>coding</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>abcdefghij</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>supercalifragilistic</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AF19" t="inlineStr">
         <is>
           <t>def length(word):
     # write your code here
@@ -3804,672 +3522,469 @@
 print(length(input()))</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG19" t="inlineStr">
         <is>
           <t>def length(word):
+    # len() counts the characters in the string
     return len(word)
 print(length(input()))</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Python - Area Function</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>A flooring calculator app computes the area of a rectangular room from its width and height, in a reusable function so the same calculation can be reused for any room in the house.
 Write a function `area(w, h)` that returns the product of `w` and `h`. Read the width and height as two whole numbers and print the result of calling `area` on them.
-### Input Format
-- Line 1: Width
-- Line 2: Height
-### Output Format
-```
-6
-```
 ### Example Walkthrough
 In the sample, the width is 2 and the height is 3. Calling `area(2, 3)` returns 6, so the program prints `6`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>function-parameters-and-arguments</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O20" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>2
 3</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>5
 5</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>0
 10</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>7
 8</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>-2
 4</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>100
 2</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE20" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>def area(w,h): return w*h
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>def area(w,h): return w*h  # area of a rectangle is width times height
 print(area(int(input()),int(input())))</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Python - Positive Function</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>A budgeting app flags whether a transaction amount is a credit or not, using a small function that answers the yes/no question so the check can be reused across the whole app.
 Write a function `pos(n)` that returns `True` if `n` is strictly greater than 0, and `False` otherwise. Read a whole number and print `Yes` if calling `pos` on it returns `True`, and `No` otherwise.
-### Input Format
-- Line 1: A whole number
-### Output Format
-```
-Yes
-```
 ### Example Walkthrough
 In the sample, the number is 1. Calling `pos(1)` returns `True` since 1 is greater than 0, so the program prints `Yes`. A value of 0 would return `False` and print `No`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>defining-and-calling-functions</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O21" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>-99</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>def pos(n): return n&gt;0
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>def pos(n): return n&gt;0  # True only when the amount is strictly positive
 print("Yes" if pos(int(input())) else "No")</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Python - Sum All Arguments</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Write a function that accepts any number of arguments using *args and returns their sum. Read a line of numbers and print their total by unpacking them into the function.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-10
-```
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Python - Group Expense Total</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>A group-expense app lets any number of friends chip in toward a shared bill, and the checkout screen has to total whatever amounts come in, whether it is one contributor or a dozen. Write a function that accepts any number of arguments using *args and returns their sum.
+Read a line of numbers and print their total by unpacking them into the function.
 ### Example Walkthrough
 In the sample, the numbers are `1 2 3 4`. Adding them gives `10`, so the program prints `10`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>function-parameters-and-arguments</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O22" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>10 -5</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>-1 -2 -3</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>100 200 300</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE22" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AF22" t="inlineStr">
         <is>
           <t>def total(*args):
     # write your code here
@@ -4478,165 +3993,161 @@
 print(total(*nums))</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG22" t="inlineStr">
         <is>
           <t>def total(*args):
+    # *args collects any number of positional arguments into a tuple
     return sum(args)
-nums = list(map(int, input().split()))
-print(total(*nums))</t>
+nums = list(map(int, input().split()))  # read however many amounts were entered
+print(total(*nums))                      # unpack the list as separate arguments</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Python - Digit Sum Function</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Write a function that returns the sum of the digits of a whole number. Read a number and print the digit sum.
-### Input Format
-- Line 1: A whole number
-### Output Format
-```
-10
-```
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Python - Loyalty Card Checksum</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>A loyalty-card app validates card numbers with a simple digit-sum checksum: it adds up every digit of the number and compares the result against a stored value.
+Write a function that returns the sum of the digits of a whole number. Read a number and print the digit sum.
 ### Example Walkthrough
 In the sample, the number is `1234`. Its digits `1`, `2`, `3`, and `4` add up to `10`, so the program prints `10`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>defining-and-calling-functions</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O23" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>1234</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>-45</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>999999</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AF23" t="inlineStr">
         <is>
           <t>def digit_sum(n):
     # write your code here
@@ -4644,632 +4155,609 @@
 print(digit_sum(int(input())))</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG23" t="inlineStr">
         <is>
           <t>def digit_sum(n):
-    n = abs(n)
+    n = abs(n)          # ignore sign, only digits matter
     total = 0
     while n &gt; 0:
-        total += n % 10
-        n //= 10
+        total += n % 10   # peel off the last digit
+        n //= 10           # drop the last digit
     return total
 print(digit_sum(int(input())))</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Python - Map to Squares</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Read a line of numbers and use map with a lambda to print each number squared, in order, separated by spaces.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-1 4 9
-```
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>A photo-editing app has a 'zoom boost' filter that squares every thumbnail's current zoom level in one batch pass, letting a whole gallery grid resize at once instead of one image at a time. Read a line of numbers and use map with a lambda to print each number squared, in order, separated by spaces.
 ### Example Walkthrough
 In the sample, the numbers are `1 2 3`. Squaring each gives `1`, `4`, and `9`, so the program prints `1 4 9`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>higher-order-functions</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O24" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>1 4 9</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>-2 5</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>4 25</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>-1 -2 -3</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>1 4 9</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>1 4 9 16 25 36 49</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>10 -10</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE24" t="inlineStr">
         <is>
           <t>100 100</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG24" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
-print(*map(lambda x: x * x, nums))</t>
+print(*map(lambda x: x * x, nums))  # map applies the lambda to every number</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Python - Filter Evens</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Read a line of numbers and use filter with a lambda to print only the even numbers, in order, separated by spaces.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-2 4 6
-```
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>A campus token counter only calls even-numbered tokens forward during its 'quick service' slot, so the display board needs to pull just the even tokens out of the full queue and show them in order. Read a line of numbers and use filter with a lambda to print only the even numbers, in order, separated by spaces.
 ### Example Walkthrough
 In the sample, the numbers are `1 2 3 4 5 6`. The even ones, in order, are `2`, `4`, and `6`, so the program prints `2 4 6`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>higher-order-functions</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O25" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>2 4 6</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>10 15 20</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>10 20</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>2 4 6</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>2 4 6</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>1 3 5</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>-2 -4 3</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>-2 -4</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE25" t="inlineStr">
         <is>
           <t>2 4 6 8 10</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG25" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
-print(*filter(lambda x: x % 2 == 0, nums))</t>
+print(*filter(lambda x: x % 2 == 0, nums))  # filter keeps only values where the lambda is True</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Python - Sort by Absolute Value</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Read a line of numbers and print them sorted by their absolute value from smallest to largest, using a lambda as the sort key.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-1 -2 -3
-```
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>An archery scoring app ranks each arrow by how close it landed to the bullseye at the center, marked `0`, regardless of whether the shot drifted left (negative) or right (positive). Read a line of numbers and print them sorted by their absolute value from smallest to largest, using a lambda as the sort key.
 ### Example Walkthrough
 In the sample, the numbers are `-3 1 -2`. Their absolute values are `3`, `1`, and `2`, so sorting from smallest to largest absolute value gives `1`, `-2`, `-3`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>higher-order-functions</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O26" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>-3 1 -2</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>1 -2 -3</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>5 -5 2</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>2 5 -5</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>-1 -2 -3</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>-1 -2 -3</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>0 -1 1</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>0 -1 1</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>10 -3 -10 3</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>-3 3 10 -10</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE26" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG26" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
-print(*sorted(nums, key=lambda x: abs(x)))</t>
+print(*sorted(nums, key=lambda x: abs(x)))  # sort using absolute value as the key</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Python - Count Vowels Function</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Write a function that returns how many vowels are in a piece of text (ignoring case). Read a line and print the vowel count.
-### Input Format
-- Line 1: A line of text
-### Output Format
-```
-5
-```
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Python - Readability Vowel Counter</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>A writing app flags text that may be hard to read aloud by counting how many vowels appear in a line of text, ignoring uppercase and lowercase differences.
+Write a function that returns how many vowels are in a piece of text (ignoring case). Read a line and print the vowel count.
 ### Example Walkthrough
 In the sample, the text is `education`. It contains `5` vowels (`e`, `u`, `a`, `i`, `o`), so the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>defining-and-calling-functions</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O27" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" t="inlineStr">
         <is>
           <t>education</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>xyz</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>AEIOU</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>bcdfg</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>The Quick Brown Fox</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>aaaaaaaaaa</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AF27" t="inlineStr">
         <is>
           <t>def count_vowels(text):
     # write your code here
@@ -5277,11 +4765,11 @@
 print(count_vowels(input()))</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG27" t="inlineStr">
         <is>
           <t>def count_vowels(text):
     count = 0
-    for ch in text.lower():
+    for ch in text.lower():   # lowercase first so case doesn't matter
         if ch in "aeiou":
             count += 1
     return count
@@ -5289,970 +4777,754 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Python - Product with Reduce</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Read a line of numbers and use functools.reduce with a lambda to print the product of all of them.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-24
-```
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>A factory's production line has several stages, each multiplying the batch by its own yield multiplier, and the plant manager needs the overall multiplier for the whole line in one shot. Read a line of numbers and use functools.reduce with a lambda to print the product of all of them.
 ### Example Walkthrough
 In the sample, the numbers are `1 2 3 4`. Multiplying them together gives `1 x 2 x 3 x 4 = 24`, so the program prints `24`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>higher-order-functions</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O28" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>2 2 2</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>0 5 6</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>-1 2 -3</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE28" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG28" t="inlineStr">
         <is>
           <t>from functools import reduce
 nums = list(map(int, input().split()))
-print(reduce(lambda a, b: a * b, nums))</t>
+print(reduce(lambda a, b: a * b, nums))  # reduce multiplies pairs together into one result</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Python - Flexible Sum</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>A donation tracker needs to add up any number of pledged amounts entered on one line, since different fundraising events may have a different number of donors and the code shouldn't need to change for each event.
 Write a function `add_all` that accepts any number of arguments using `*args` and returns their sum. Read a line of space-separated whole numbers, pass them all to `add_all`, and print the result.
-### Input Format
-- Line 1: Space-separated whole numbers
-### Output Format
-```
-6
-```
 ### Example Walkthrough
 In the sample, the numbers are `1 2 3`. Calling `add_all(1, 2, 3)` returns 6, so the program prints `6`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>function-parameters-and-arguments</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O29" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>0 -1 1</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>10 20</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>100 200 300</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>-5 -5</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE29" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>def add_all(*nums): return sum(nums)
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>def add_all(*nums): return sum(nums)  # *nums collects any number of pledges into a tuple
 nums=[int(x) for x in input().split()]
-print(add_all(*nums))</t>
+print(add_all(*nums))                  # unpack the list as separate arguments</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Python - Lambda Sort</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>A word-game app arranges the words a player types from shortest to longest to build a word ladder, using a lambda as the sort key instead of writing a separate function. Words of the same length keep their original order.
 Write a program that reads a line of space-separated words and prints them sorted from shortest to longest (by number of characters), separated by single spaces, using `sort` with a `lambda` key.
-### Input Format
-- Line 1: Space-separated words
-### Output Format
-```
-b aa ccc
-```
 ### Example Walkthrough
 In the sample, the words are `aa b ccc` with lengths 2, 1, and 3. Sorting by length gives `b` (length 1), `aa` (length 2), `ccc` (length 3), so the program prints `b aa ccc`.
 ### Constraints
 - The input is a valid line of space-separated words.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>lambda-functions</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O30" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" t="inlineStr">
         <is>
           <t>aa b ccc</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>b aa ccc</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>python java c</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>c java python</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>same size</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>same size</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>a ab abc abcd</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>a ab abc abcd</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>zz yyy xx</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>zz xx yyy</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>red blue green</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE30" t="inlineStr">
         <is>
           <t>red blue green</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>words=input().split(); words.sort(key=lambda w:len(w)); print(*words)</t>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>words=input().split(); words.sort(key=lambda w:len(w)); print(*words)  # sort words by length using a lambda key</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Python - Map Cubes</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>A math visualizer computes the cube of every number a student enters to plot how fast values grow, applying a `cube` function to the whole list at once using Python's `map`.
 Write a function `cube(n)` that returns `n` raised to the power 3. Read a line of space-separated whole numbers, use `map` to apply `cube` to each one, and print the results separated by single spaces.
-### Input Format
-- Line 1: Space-separated whole numbers
-### Output Format
-```
-1 8 27
-```
 ### Example Walkthrough
 In the sample, the numbers are `1 2 3`. Cubing each gives 1, 8, and 27, so the program prints `1 8 27`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>higher-order-functions</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O31" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>1 8 27</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>-1 2</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>-1 8</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>10 0</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>1000 0</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>2 4</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>8 64</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>-2 -3</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE31" t="inlineStr">
         <is>
           <t>-8 -27</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>def cube(n): return n**3
-print(*map(cube, map(int,input().split())))</t>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>def cube(n): return n**3  # n raised to the power 3
+print(*map(cube, map(int,input().split())))  # map applies cube to every number read</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Python - Recursive Digit Sum</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Write a recursive function that returns the sum of the digits of a whole number (no loops). Read a number and print the digit sum.
-### Input Format
-- Line 1: A whole number
-### Output Format
-```
-10
-```
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A banking app's fraud check reduces a transaction PIN to a single check digit by recursively summing its digits, a lightweight first pass before the full verification runs. Write a recursive function that returns the sum of the digits of a whole number (no loops). Read a number and print the digit sum.
 ### Example Walkthrough
 In the sample, the number is `1234`. Its digits sum to `1 + 2 + 3 + 4 = 10`, so the program prints `10`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>recursion</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O32" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P32" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>1234</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>9999</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>-45</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>999999</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE32" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AF32" t="inlineStr">
         <is>
           <t>def digit_sum(n):
     # write your code here
@@ -6260,174 +5532,169 @@
 print(digit_sum(abs(int(input()))))</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG32" t="inlineStr">
         <is>
           <t>def digit_sum(n):
+    # Base case: a single digit is its own digit sum
     if n &lt; 10:
         return n
+    # Recursive case: last digit plus the digit sum of the rest
     return n % 10 + digit_sum(n // 10)
-print(digit_sum(abs(int(input()))))</t>
+print(digit_sum(abs(int(input()))))  # ignore sign, only digits matter</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Python - Recursive Power</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Write a recursive function that returns a raised to the power b (b is a non-negative whole number). Read a and b and print a to the power b.
-### Input Format
-- Line 1: a, the base
-- Line 2: b, the exponent
-### Output Format
-```
-1024
-```
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>A savings app projects how a fixed growth multiplier compounds an investment year after year, and the projection screen needs to raise that multiplier to however many years the user plans to invest. Write a recursive function that returns a raised to the power b (b is a non-negative whole number). Read a and b and print a to the power b.
 ### Example Walkthrough
 In the sample, `a` is `2` and `b` is `10`. Computing `2` raised to the power `10` gives `1024`, so the program prints `1024`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>recursion</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O33" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P33" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" t="inlineStr">
         <is>
           <t>2
 10</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>5
 0</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>3
 4</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>1
 5</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>-2
 3</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>10
 0</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AF33" t="inlineStr">
         <is>
           <t>def power(a, b):
     # write your code here
@@ -6437,11 +5704,13 @@
 print(power(base, exp))</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG33" t="inlineStr">
         <is>
           <t>def power(a, b):
+    # Base case: anything to the power 0 is 1
     if b == 0:
         return 1
+    # Recursive case: multiply a by itself, one less exponent each time
     return a * power(a, b - 1)
 base = int(input())
 exp = int(input())
@@ -6449,164 +5718,157 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Python - Recursive GCD</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Write a recursive function that returns the greatest common divisor of two numbers. Read two numbers and print their GCD.
-### Input Format
-- Line 1: First number
-- Line 2: Second number
-### Output Format
-```
-6
-```
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>A recipe app rewrites ingredient ratios in their simplest form, so a batch that calls for 12 cups of flour to 18 cups of water can be shown as the smallest equivalent ratio. Write a recursive function that returns the greatest common divisor of two numbers. Read two numbers and print their GCD.
 ### Example Walkthrough
 In the sample, the numbers are `12` and `18`. Their greatest common divisor is `6`, so the program prints `6`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>recursion</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O34" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" t="inlineStr">
         <is>
           <t>12
 18</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>17
 5</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>100
 25</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>7
 7</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>1000
 999</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE34" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AF34" t="inlineStr">
         <is>
           <t>def gcd(a, b):
     # write your code here
@@ -6616,11 +5878,13 @@
 print(gcd(x, y))</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG34" t="inlineStr">
         <is>
           <t>def gcd(a, b):
+    # Base case: when b reaches 0, a is the greatest common divisor
     if b == 0:
         return a
+    # Recursive case: Euclid's algorithm, repeat with (b, a mod b)
     return gcd(b, a % b)
 x = int(input())
 y = int(input())
@@ -6628,492 +5892,473 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Python - Mini Calculator</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Store the operations +, -, and * in a dictionary of lambdas. Read a number, an operator, and a second number, then print the result by looking up the operator.
-### Input Format
-- Line 1: First number
-- Line 2: An operator (+, -, or *)
-- Line 3: Second number
-### Output Format
-```
-10
-```
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>A campus calculator kiosk offers just the three basic operators, +, -, and *, and looks up whichever one the student taps instead of running a long chain of if-elif checks. Store the operations in a dictionary of lambdas. Read a number, an operator, and a second number, then print the result by looking up the operator.
 ### Example Walkthrough
 In the sample, the numbers are `6` and `4` with the operator `+`. Looking up `+` in the dictionary and applying it gives `6 + 4 = 10`, so the program prints `10`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>lambda-functions</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O35" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P35" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>1</v>
+      </c>
+      <c r="R35" t="inlineStr">
         <is>
           <t>6
 +
 4</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>10
 -
 3</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>5
 *
 6</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>0
 +
 0</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>-5
 -
 -3</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>1
 *
 1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>100
 +
 200</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE35" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG35" t="inlineStr">
         <is>
           <t>ops = {
+    # dictionary of lambdas, one per operator symbol
     "+": lambda x, y: x + y,
     "-": lambda x, y: x - y,
     "*": lambda x, y: x * y,
 }
 a = int(input())
-op = input()
+op = input()          # the operator symbol chosen by the user
 b = int(input())
-print(ops[op](a, b))</t>
+print(ops[op](a, b))  # look up the matching lambda and call it</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Python - Sum of Even Squares</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Read a line of numbers. Using filter to keep the even numbers and map to square them, print the sum of the squares of the even numbers.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-20
-```
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>A fitness tracker logs calories burned in each workout interval, and the weekly report highlights consistency by squaring only the even-numbered calorie counts and adding them up. Read a line of numbers. Using filter to keep the even numbers and map to square them, print the sum of the squares of the even numbers.
 ### Example Walkthrough
 In the sample, the numbers are `1 2 3 4`. The even numbers are `2` and `4`, whose squares are `4` and `16`, summing to `20`, so the program prints `20`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>higher-order-functions</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O36" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>2 4 6</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>1 3 5</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>-2 -4 3</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>10 -10 5</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG36" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
-evens = filter(lambda x: x % 2 == 0, nums)
-print(sum(map(lambda x: x * x, evens)))</t>
+evens = filter(lambda x: x % 2 == 0, nums)   # keep only the even numbers
+print(sum(map(lambda x: x * x, evens)))       # square each even number, then add them up</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Python - Recursive String Reverse</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Write a recursive function that returns a string reversed (no loops and no slicing tricks other than peeling one character at a time). Read a word and print it reversed.
-### Input Format
-- Line 1: A word
-### Output Format
-```
-olleh
-```
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>A messaging app hides a playful easter egg: type '/reverse' before a word and it echoes the word back spelled backwards. Write a recursive function that returns a string reversed (no loops and no slicing tricks other than peeling one character at a time). Read a word and print it reversed.
 ### Example Walkthrough
 In the sample, the word is `hello`. Reversing it one character at a time gives `olleh`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>recursion</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O37" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>1</v>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>olleh</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>abcde</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>edcba</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>ab</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>ba</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>racecar</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>racecar</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>supercalifragilistic</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE37" t="inlineStr">
         <is>
           <t>citsiligarfilacrepus</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AF37" t="inlineStr">
         <is>
           <t>def reverse(s):
     # write your code here
@@ -7121,166 +6366,162 @@
 print(reverse(input()))</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG37" t="inlineStr">
         <is>
           <t>def reverse(s):
+    # Base case: a string of 0 or 1 characters is already reversed
     if len(s) &lt;= 1:
         return s
+    # Recursive case: reverse the rest, then place the first char at the end
     return reverse(s[1:]) + s[0]
 print(reverse(input()))</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Python - Recursive Palindrome</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Write a recursive function that returns whether a word is a palindrome. Read a word and print 'Yes' if it is a palindrome, otherwise 'No'.
-### Input Format
-- Line 1: A word
-### Output Format
-```
-Yes
-```
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>A word-game app challenges players to spot palindromes, words that read the same forwards and backwards, before the timer runs out. Write a recursive function that returns whether a word is a palindrome. Read a word and print 'Yes' if it is a palindrome, otherwise 'No'.
 ### Example Walkthrough
 In the sample, the word is `racecar`. Since it reads the same forwards and backwards, the program prints `Yes`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>recursion</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O38" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P38" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>racecar</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>ab</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>noon</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>abcba</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE38" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AF38" t="inlineStr">
         <is>
           <t>def is_palindrome(s):
     # write your code here
@@ -7288,498 +6529,481 @@
 print("Yes" if is_palindrome(input()) else "No")</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG38" t="inlineStr">
         <is>
           <t>def is_palindrome(s):
+    # Base case: 0 or 1 characters always reads the same both ways
     if len(s) &lt;= 1:
         return True
+    # Recursive case: ends must match, and the inner part must also be a palindrome
     return s[0] == s[-1] and is_palindrome(s[1:-1])
 print("Yes" if is_palindrome(input()) else "No")</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Python - Recursive Sum</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>A staircase-climbing app calculates the total step count by adding every step number from 1 up to N, but the developer wants practice with recursion, so the function calls itself with a smaller N each time instead of using a loop.
 Write a function `total(n)` that returns 0 if `n` is 0 or less, and otherwise returns `n` plus the result of calling `total(n - 1)`. Read a whole number and print the result of calling `total` on it.
-### Input Format
-- Line 1: N
-### Output Format
-```
-15
-```
 ### Example Walkthrough
 In the sample, N is 5. `total(5)` calls `5 + total(4)`, which calls `4 + total(3)`, and so on down to `total(0)` which returns 0; adding everything back up gives 5+4+3+2+1 = 15, so the program prints `15`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>recursion</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O39" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P39" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>1</v>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE39" t="inlineStr">
         <is>
           <t>5050</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>def total(n): return 0 if n&lt;=0 else n+total(n-1)
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>def total(n): return 0 if n&lt;=0 else n+total(n-1)  # base case 0, else add n to total(n-1)
 print(total(int(input())))</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Python - Scoped Counter</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>A gym turnstile counts each entry using a counter that is set up once when the gym opens. Every time someone taps in, an inner function increments a count that only it can access, thanks to closures and the `nonlocal` keyword, and the front desk display shows the count after the most recent tap.
 Write a function `make_counter()` that creates a local variable `count` starting at 0 and returns an inner function `inc` which increments `count` (using `nonlocal`) and returns the new value. Read a whole number N, call the returned `inc` function N times, and print the value returned by the last call.
-### Input Format
-- Line 1: N, the number of taps
-### Output Format
-```
-3
-```
 ### Example Walkthrough
 In the sample, N is 3. Calling the counter's `inc` function three times increments the hidden count from 0 to 1, then 2, then 3, so the last call returns 3 and the program prints `3`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>variable-scope-and-legb</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O40" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P40" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>1</v>
+      </c>
+      <c r="R40" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE40" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG40" t="inlineStr">
         <is>
           <t>def make_counter():
- count=0
+ count=0                                    # counter starts at zero, created once
  def inc():
-  nonlocal count; count+=1; return count
- return inc
+  nonlocal count; count+=1; return count    # nonlocal lets inner function modify outer count
+ return inc                                  # closure: returns a function tied to this count
 n=int(input()); c=make_counter(); last=0
-for _ in range(n): last=c()
+for _ in range(n): last=c()                  # tap in n times, each call increments the shared counter
 print(last)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Python - Documented Power</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>A scientific calculator app exposes a `power` function with a clear docstring explaining what it does, so other developers can call `help(power)` to learn its behavior without reading the implementation. The function raises a base number to an exponent.
 Write a function `power(base, exponent)` with a docstring describing that it returns `base` raised to `exponent`, and have it return `base ** exponent`. Read the base and the exponent as two whole numbers and print the result of calling `power` on them.
-### Input Format
-- Line 1: Base
-- Line 2: Exponent
-### Output Format
-```
-8
-```
 ### Example Walkthrough
 In the sample, the base is 2 and the exponent is 3. Calling `power(2, 3)` returns 2 to the power of 3, which is 8, so the program prints `8`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>functions</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>docstrings-and-clean-code</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O41" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P41" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>1</v>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>2
 3</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>5
 0</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>10
 2</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>-2
 3</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>3
 4</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>1
 99</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG41" t="inlineStr">
         <is>
           <t>def power(base, exponent):
- """Return base raised to exponent."""
+ """Return base raised to exponent."""       # docstring: explains the function without reading its body
  return base**exponent
 print(power(int(input()),int(input())))</t>
         </is>
